--- a/Result/profitability/5438.xlsx
+++ b/Result/profitability/5438.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.96</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3137500000000001</v>
+        <v>0.1675</v>
       </c>
       <c r="N2" t="n">
-        <v>17.21875</v>
+        <v>16.87625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3087500000000001</v>
+        <v>0.20625</v>
       </c>
       <c r="N3" t="n">
-        <v>19.20125</v>
+        <v>18.74</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.79</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3500000000000001</v>
+        <v>0.2887500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>20.72</v>
+        <v>20.55125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3462500000000001</v>
+        <v>0.3075000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>22.24125</v>
+        <v>22.07875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4400000000000001</v>
+        <v>0.3150000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>24.05</v>
+        <v>23.865</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0.42125</v>
+        <v>0.40125</v>
       </c>
       <c r="N7" t="n">
-        <v>26.03875</v>
+        <v>25.9375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>0.73</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5375000000000001</v>
+        <v>0.5225000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>27.2725</v>
+        <v>27.75625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>210</v>
+      </c>
+      <c r="D75" t="n">
+        <v>180</v>
+      </c>
+      <c r="E75" t="n">
+        <v>30</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-16.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-29</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.14875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.0575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.869999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.377560975609756</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>6.199999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.300000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08430609597924776</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
